--- a/output/pdf_financials_xlsx/ACDC.xlsx
+++ b/output/pdf_financials_xlsx/ACDC.xlsx
@@ -1949,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.600461</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.600461</v>
       </c>
     </row>
     <row r="93">
@@ -3103,7 +3103,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3368,7 +3372,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ACDC.xlsx
+++ b/output/pdf_financials_xlsx/ACDC.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.217095</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.992001</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.217095</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.175</v>
+        <v>1.167001</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.465267</v>
+        <v>0.248172</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.017809</v>
+        <v>0.025808</v>
       </c>
     </row>
     <row r="49">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ACDC.xlsx
+++ b/output/pdf_financials_xlsx/ACDC.xlsx
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="68">
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.027536</v>
+        <v>0.052536</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.025315</v>
+        <v>0.050315</v>
       </c>
     </row>
     <row r="69">
